--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.85654601683909</v>
+        <v>9.564188727736353</v>
       </c>
       <c r="D2" t="n">
-        <v>58.61322089913776</v>
+        <v>9.524648396109885</v>
       </c>
       <c r="E2" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F2" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.37556175265174</v>
+        <v>8.348528784805909</v>
       </c>
       <c r="D3" t="n">
-        <v>51.1166578647561</v>
+        <v>8.306456903022866</v>
       </c>
       <c r="E3" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F3" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.50265125584358</v>
+        <v>6.094180829074582</v>
       </c>
       <c r="D4" t="n">
-        <v>37.19386542684097</v>
+        <v>6.044003131861658</v>
       </c>
       <c r="E4" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F4" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.05605188992042</v>
+        <v>2.446608432112069</v>
       </c>
       <c r="D5" t="n">
-        <v>14.81026702679705</v>
+        <v>2.406668391854521</v>
       </c>
       <c r="E5" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F5" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.14281864879992</v>
+        <v>8.635708030429988</v>
       </c>
       <c r="D6" t="n">
-        <v>53.06969805328861</v>
+        <v>8.623825933659401</v>
       </c>
       <c r="E6" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F6" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.72032253890294</v>
+        <v>4.992052412571728</v>
       </c>
       <c r="D7" t="n">
-        <v>30.87626935698405</v>
+        <v>5.017393770509908</v>
       </c>
       <c r="E7" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F7" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.68147581252968</v>
+        <v>10.02323981953607</v>
       </c>
       <c r="D8" t="n">
-        <v>61.82791965146792</v>
+        <v>10.04703694336354</v>
       </c>
       <c r="E8" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F8" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.57310736117706</v>
+        <v>6.105629946191272</v>
       </c>
       <c r="D9" t="n">
-        <v>23.71290290703979</v>
+        <v>3.853346722393966</v>
       </c>
       <c r="E9" t="n">
-        <v>14.85061363642086</v>
+        <v>2.41322471591839</v>
       </c>
       <c r="F9" t="n">
-        <v>16.17280855129661</v>
+        <v>2.628081389585699</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
